--- a/APPT/data/output/Final_Production_Plan_2026-01-20.xlsx
+++ b/APPT/data/output/Final_Production_Plan_2026-01-20.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1900" uniqueCount="329">
   <si>
     <t>Production Line</t>
   </si>
@@ -76,24 +76,21 @@
     <t>MRP Status</t>
   </si>
   <si>
+    <t>INC1</t>
+  </si>
+  <si>
+    <t>INC4</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
+    <t>INT2</t>
+  </si>
+  <si>
     <t>INC2</t>
   </si>
   <si>
-    <t>INC1</t>
-  </si>
-  <si>
-    <t>INC4</t>
-  </si>
-  <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>INT2</t>
-  </si>
-  <si>
-    <t>910735874 + 910739653</t>
-  </si>
-  <si>
     <t>910739815</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>910741730</t>
   </si>
   <si>
-    <t>910739741 + 910739800</t>
-  </si>
-  <si>
     <t>AUTO_2</t>
   </si>
   <si>
@@ -145,9 +139,21 @@
     <t>910741865</t>
   </si>
   <si>
+    <t>910735874</t>
+  </si>
+  <si>
+    <t>910739653</t>
+  </si>
+  <si>
     <t>910739590</t>
   </si>
   <si>
+    <t>910739741</t>
+  </si>
+  <si>
+    <t>910739800</t>
+  </si>
+  <si>
     <t>910741725</t>
   </si>
   <si>
@@ -157,33 +163,33 @@
     <t>910741819</t>
   </si>
   <si>
+    <t>83900263</t>
+  </si>
+  <si>
+    <t>83900262</t>
+  </si>
+  <si>
+    <t>95619314</t>
+  </si>
+  <si>
+    <t>80880903</t>
+  </si>
+  <si>
+    <t>83900259</t>
+  </si>
+  <si>
+    <t>80880904</t>
+  </si>
+  <si>
     <t>80750818</t>
   </si>
   <si>
-    <t>83900263</t>
-  </si>
-  <si>
-    <t>83900262</t>
-  </si>
-  <si>
-    <t>95619314</t>
+    <t>80750816</t>
   </si>
   <si>
     <t>80750817</t>
   </si>
   <si>
-    <t>80880903</t>
-  </si>
-  <si>
-    <t>83900259</t>
-  </si>
-  <si>
-    <t>80880904</t>
-  </si>
-  <si>
-    <t>80750816</t>
-  </si>
-  <si>
     <t>80880895</t>
   </si>
   <si>
@@ -193,82 +199,85 @@
     <t>80880883</t>
   </si>
   <si>
+    <t>H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>HC BASE</t>
+  </si>
+  <si>
+    <t>H&amp;S SS</t>
+  </si>
+  <si>
+    <t>H&amp;S AHF</t>
+  </si>
+  <si>
     <t>H&amp;S SS 2in1</t>
   </si>
   <si>
-    <t>H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>HC BASE</t>
+    <t>H&amp;S Shiny Black 2in1</t>
   </si>
   <si>
     <t>H&amp;S Menthol Fresh</t>
   </si>
   <si>
-    <t>H&amp;S SS</t>
-  </si>
-  <si>
-    <t>H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>H&amp;S Shiny Black 2in1</t>
-  </si>
-  <si>
     <t>H&amp;S CM</t>
   </si>
   <si>
     <t>H&amp;S AP 2in1</t>
   </si>
   <si>
-    <t>CI610</t>
-  </si>
-  <si>
-    <t>CI611</t>
-  </si>
-  <si>
-    <t>CI612</t>
-  </si>
-  <si>
-    <t>CI613</t>
+    <t>CI624</t>
+  </si>
+  <si>
+    <t>CI625</t>
+  </si>
+  <si>
+    <t>CI626</t>
   </si>
   <si>
     <t>REP01-0120</t>
   </si>
   <si>
-    <t>CI615</t>
-  </si>
-  <si>
-    <t>CI616</t>
-  </si>
-  <si>
-    <t>CI617</t>
-  </si>
-  <si>
-    <t>CI618</t>
-  </si>
-  <si>
-    <t>CI619</t>
+    <t>CI629</t>
+  </si>
+  <si>
+    <t>CI630</t>
+  </si>
+  <si>
+    <t>CI631</t>
+  </si>
+  <si>
+    <t>CI632</t>
   </si>
   <si>
     <t>REP02-0120</t>
   </si>
   <si>
-    <t>CI620</t>
-  </si>
-  <si>
-    <t>CI621</t>
-  </si>
-  <si>
-    <t>CI622</t>
-  </si>
-  <si>
-    <t>CI624</t>
-  </si>
-  <si>
-    <t>CI625</t>
+    <t>CI634</t>
+  </si>
+  <si>
+    <t>CI635</t>
+  </si>
+  <si>
+    <t>CI636</t>
+  </si>
+  <si>
+    <t>CI639</t>
+  </si>
+  <si>
+    <t>CI640</t>
+  </si>
+  <si>
+    <t>CI642</t>
+  </si>
+  <si>
+    <t>CI643</t>
+  </si>
+  <si>
+    <t>CI623</t>
   </si>
   <si>
     <t>CI627</t>
@@ -277,39 +286,42 @@
     <t>CI628</t>
   </si>
   <si>
-    <t>CI614</t>
-  </si>
-  <si>
-    <t>CI623</t>
-  </si>
-  <si>
-    <t>CI626</t>
-  </si>
-  <si>
-    <t>CI629</t>
+    <t>CI633</t>
+  </si>
+  <si>
+    <t>CI637</t>
+  </si>
+  <si>
+    <t>CI638</t>
+  </si>
+  <si>
+    <t>CI641</t>
+  </si>
+  <si>
+    <t>CI644</t>
+  </si>
+  <si>
+    <t>21470269</t>
+  </si>
+  <si>
+    <t>21453170</t>
+  </si>
+  <si>
+    <t>21422079</t>
+  </si>
+  <si>
+    <t>21417344</t>
   </si>
   <si>
     <t>21432817</t>
   </si>
   <si>
-    <t>21470269</t>
-  </si>
-  <si>
-    <t>21453170</t>
+    <t>21055594</t>
   </si>
   <si>
     <t>90275009</t>
   </si>
   <si>
-    <t>21422079</t>
-  </si>
-  <si>
-    <t>21417344</t>
-  </si>
-  <si>
-    <t>21055594</t>
-  </si>
-  <si>
     <t>90947730</t>
   </si>
   <si>
@@ -334,49 +346,64 @@
     <t>Dual</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>TK#_25_# + TK#_4_#</t>
-  </si>
-  <si>
-    <t>TK#_22_# [Wash 20m] + TK#_17_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_11_# [Wash 20m] + TK#_25_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_17_# + TK#_22_#</t>
+    <t>TK#_5_# [Wash 20m] + TK#_13_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_23_# + TK#_7_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_13_# + TK#_5_#</t>
   </si>
   <si>
     <t>HC Base Tank</t>
   </si>
   <si>
-    <t>TK#_11_# + TK#_25_#</t>
-  </si>
-  <si>
-    <t>TK#_19_# [Wash 20m] + TK#_16_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_17_# [Wash 20m] + TK#_22_# [Wash 20m]</t>
+    <t>TK#_7_# + TK#_23_#</t>
+  </si>
+  <si>
+    <t>TK#_5_# + TK#_2_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_5_# + TK#_2_#</t>
   </si>
   <si>
     <t>TK#_53_#</t>
   </si>
   <si>
+    <t>TK#_9_# [Wash 20m] + TK#_7_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_9_# + TK#_7_#</t>
+  </si>
+  <si>
     <t>TK#_53_# [Wash 20m]</t>
   </si>
   <si>
-    <t>TK#_4_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_10_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_18_# [Wash 20m]</t>
+    <t>TK#_21_#</t>
+  </si>
+  <si>
+    <t>TK#_2_#</t>
+  </si>
+  <si>
+    <t>TK#_21_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_9_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_13_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_6_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_26_# [Wash 20m]</t>
   </si>
   <si>
     <t>LOW: SLS</t>
@@ -730,16 +757,13 @@
     <t>C</t>
   </si>
   <si>
-    <t>CI610: H&amp;S SS 2in1</t>
-  </si>
-  <si>
-    <t>CI611: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI612: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI613: H&amp;S Daily Clean Libra</t>
+    <t>CI624: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI625: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI626: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>WASHOUT</t>
@@ -748,82 +772,85 @@
     <t>REP01-0120: HC BASE</t>
   </si>
   <si>
-    <t>CI615: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI616: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI617: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI618: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI619: H&amp;S Menthol Fresh</t>
+    <t>CI629: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI630: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI631: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI632: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>REP02-0120: HC BASE</t>
   </si>
   <si>
-    <t>CI620: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI621: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI622: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI624: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI625: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI627: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI628: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI614: H&amp;S Shiny Black 2in1</t>
-  </si>
-  <si>
-    <t>CI623: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>CI626: H&amp;S AP 2in1</t>
-  </si>
-  <si>
-    <t>CI629: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>TK#_4_#</t>
-  </si>
-  <si>
-    <t>TK#_10_#</t>
-  </si>
-  <si>
-    <t>TK#_11_#</t>
-  </si>
-  <si>
-    <t>TK#_16_#</t>
-  </si>
-  <si>
-    <t>TK#_17_#</t>
-  </si>
-  <si>
-    <t>TK#_18_#</t>
-  </si>
-  <si>
-    <t>TK#_19_#</t>
-  </si>
-  <si>
-    <t>TK#_22_#</t>
-  </si>
-  <si>
-    <t>TK#_25_#</t>
+    <t>CI634: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI635: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI636: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI639: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI640: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI642: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI643: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI623: H&amp;S SS 2in1</t>
+  </si>
+  <si>
+    <t>CI627: H&amp;S SS 2in1</t>
+  </si>
+  <si>
+    <t>CI628: H&amp;S Shiny Black 2in1</t>
+  </si>
+  <si>
+    <t>CI633: H&amp;S Menthol Fresh</t>
+  </si>
+  <si>
+    <t>CI637: H&amp;S Menthol Fresh</t>
+  </si>
+  <si>
+    <t>CI638: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>CI641: H&amp;S AP 2in1</t>
+  </si>
+  <si>
+    <t>CI644: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>TK#_5_#</t>
+  </si>
+  <si>
+    <t>TK#_6_#</t>
+  </si>
+  <si>
+    <t>TK#_7_#</t>
+  </si>
+  <si>
+    <t>TK#_9_#</t>
+  </si>
+  <si>
+    <t>TK#_13_#</t>
+  </si>
+  <si>
+    <t>TK#_23_#</t>
+  </si>
+  <si>
+    <t>TK#_26_#</t>
   </si>
   <si>
     <t>2026-01-21 17:30</t>
@@ -886,58 +913,58 @@
     <t>2026-01-22 03:00</t>
   </si>
   <si>
-    <t>CI610: H&amp;S SS 2in1 | CI614: H&amp;S Shiny Black 2in1</t>
-  </si>
-  <si>
-    <t>CI614: H&amp;S Shiny Black 2in1 | CI629: H&amp;S SS</t>
+    <t>WASHOUT (20m) | CI627: H&amp;S SS 2in1</t>
+  </si>
+  <si>
+    <t>CI630: H&amp;S Daily Clean Libra | CI632: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI632: H&amp;S Daily Clean Libra | CI635: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI635: H&amp;S Daily Clean Libra | CI640: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI640: H&amp;S Daily Clean Libra | CI643: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI624: H&amp;S Daily Clean Libra | CI626: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI626: H&amp;S Daily Clean Libra | CI630: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>WASHOUT (20m)</t>
   </si>
   <si>
-    <t>CI612: H&amp;S Daily Cool Libra | CI615: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI615: H&amp;S Daily Cool Libra | WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI615: H&amp;S Daily Cool Libra | CI618: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI618: H&amp;S Daily Clean Libra | CI621: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI621: H&amp;S Daily Clean Libra | CI625: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI625: H&amp;S Daily Clean Libra | CI628: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI611: H&amp;S Daily Clean Libra | CI613: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI613: H&amp;S Daily Clean Libra | CI616: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI616: H&amp;S Daily Clean Libra | WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI616: H&amp;S Daily Clean Libra | CI619: H&amp;S Menthol Fresh</t>
-  </si>
-  <si>
-    <t>CI619: H&amp;S Menthol Fresh | CI622: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI619: H&amp;S Menthol Fresh | CI622: H&amp;S Daily Clean Libra | CI624: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI619: H&amp;S Menthol Fresh | CI624: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI610: H&amp;S SS 2in1 | CI612: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI610: H&amp;S SS 2in1 | CI612: H&amp;S Daily Cool Libra | CI615: H&amp;S Daily Cool Libra</t>
+    <t>CI625: H&amp;S Daily Cool Libra | CI629: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI629: H&amp;S Daily Cool Libra | CI631: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI631: H&amp;S Daily Cool Libra | CI636: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI636: H&amp;S Daily Clean Libra | CI639: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI636: H&amp;S Daily Clean Libra | CI633: H&amp;S Menthol Fresh</t>
+  </si>
+  <si>
+    <t>CI636: H&amp;S Daily Clean Libra | CI639: H&amp;S Daily Clean Libra | CI633: H&amp;S Menthol Fresh</t>
+  </si>
+  <si>
+    <t>CI626: H&amp;S Daily Clean Libra | CI637: H&amp;S Menthol Fresh</t>
+  </si>
+  <si>
+    <t>CI623: H&amp;S SS 2in1 | WASHOUT (20m)</t>
+  </si>
+  <si>
+    <t>CI623: H&amp;S SS 2in1 | CI628: H&amp;S Shiny Black 2in1</t>
+  </si>
+  <si>
+    <t>CI628: H&amp;S Shiny Black 2in1 | CI644: H&amp;S SS</t>
   </si>
   <si>
     <t>Sr.No</t>
@@ -1341,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="21" width="15.7109375" customWidth="1"/>
@@ -1414,55 +1441,55 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I2">
-        <v>2.8174</v>
+        <v>4.4185</v>
       </c>
       <c r="J2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L2" s="2">
-        <v>46041.39375</v>
+        <v>46041.79166666666</v>
       </c>
       <c r="M2">
         <v>90</v>
       </c>
       <c r="N2" s="2">
-        <v>46041.45625</v>
+        <v>46041.85416666666</v>
       </c>
       <c r="O2">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="P2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Q2" s="2">
-        <v>46041.53958333333</v>
+        <v>46041.96180555555</v>
       </c>
       <c r="R2" s="2">
-        <v>46042.57569444444</v>
+        <v>46042.47847222222</v>
       </c>
       <c r="S2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1473,60 +1500,60 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I3">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="J3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L3" s="2">
-        <v>46041.79166666666</v>
+        <v>46041.85416666666</v>
       </c>
       <c r="M3">
         <v>90</v>
       </c>
       <c r="N3" s="2">
-        <v>46041.85416666666</v>
+        <v>46041.91666666666</v>
       </c>
       <c r="O3">
-        <v>155</v>
+        <v>701</v>
       </c>
       <c r="P3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Q3" s="2">
-        <v>46041.96180555555</v>
+        <v>46042.40347222222</v>
       </c>
       <c r="R3" s="2">
-        <v>46042.47847222222</v>
+        <v>46042.61666666667</v>
       </c>
       <c r="S3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1538,113 +1565,113 @@
         <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I4">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="J4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L4" s="2">
-        <v>46041.85416666666</v>
+        <v>46041.91666666666</v>
       </c>
       <c r="M4">
         <v>90</v>
       </c>
       <c r="N4" s="2">
-        <v>46041.91666666666</v>
+        <v>46041.97916666666</v>
       </c>
       <c r="O4">
-        <v>701</v>
+        <v>719</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q4" s="2">
-        <v>46042.40347222222</v>
+        <v>46042.47847222222</v>
       </c>
       <c r="R4" s="2">
-        <v>46042.61666666667</v>
+        <v>46042.6625</v>
       </c>
       <c r="S4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I5">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L5" s="2">
-        <v>46041.91666666666</v>
+        <v>46042.35</v>
       </c>
       <c r="M5">
         <v>90</v>
       </c>
       <c r="N5" s="2">
-        <v>46041.97916666666</v>
+        <v>46042.4125</v>
       </c>
       <c r="O5">
-        <v>719</v>
+        <v>120</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q5" s="2">
-        <v>46042.47847222222</v>
+        <v>46042.49583333333</v>
       </c>
       <c r="R5" s="2">
-        <v>46042.6625</v>
+        <v>46042.5375</v>
       </c>
       <c r="S5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -1656,54 +1683,54 @@
         <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I6">
-        <v>2.2948</v>
+        <v>4.4163</v>
       </c>
       <c r="J6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L6" s="2">
-        <v>46042.3125</v>
+        <v>46042.45138888889</v>
       </c>
       <c r="M6">
         <v>90</v>
       </c>
       <c r="N6" s="2">
-        <v>46042.375</v>
+        <v>46042.51388888889</v>
       </c>
       <c r="O6">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q6" s="2">
-        <v>46042.49583333333</v>
+        <v>46042.61666666667</v>
       </c>
       <c r="R6" s="2">
-        <v>46042.5375</v>
+        <v>46042.83055555556</v>
       </c>
       <c r="S6" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
@@ -1715,49 +1742,49 @@
         <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I7">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="J7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L7" s="2">
-        <v>46042.38888888889</v>
+        <v>46042.51388888889</v>
       </c>
       <c r="M7">
         <v>90</v>
       </c>
       <c r="N7" s="2">
-        <v>46042.45138888889</v>
+        <v>46042.57638888889</v>
       </c>
       <c r="O7">
-        <v>238</v>
+        <v>124</v>
       </c>
       <c r="P7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Q7" s="2">
-        <v>46042.61666666667</v>
+        <v>46042.6625</v>
       </c>
       <c r="R7" s="2">
-        <v>46042.83055555556</v>
+        <v>46042.84583333333</v>
       </c>
       <c r="S7" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1768,60 +1795,60 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I8">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L8" s="2">
-        <v>46042.45138888889</v>
+        <v>46042.57638888889</v>
       </c>
       <c r="M8">
         <v>90</v>
       </c>
       <c r="N8" s="2">
-        <v>46042.51388888889</v>
+        <v>46042.63888888889</v>
       </c>
       <c r="O8">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="Q8" s="2">
-        <v>46042.6625</v>
+        <v>46042.83055555556</v>
       </c>
       <c r="R8" s="2">
-        <v>46042.84583333333</v>
+        <v>46043.37708333333</v>
       </c>
       <c r="S8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1833,349 +1860,349 @@
         <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I9">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="J9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L9" s="2">
-        <v>46042.51388888889</v>
+        <v>46042.63888888889</v>
       </c>
       <c r="M9">
         <v>90</v>
       </c>
       <c r="N9" s="2">
-        <v>46042.57638888889</v>
+        <v>46042.70138888889</v>
       </c>
       <c r="O9">
-        <v>366</v>
+        <v>208</v>
       </c>
       <c r="P9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Q9" s="2">
-        <v>46042.83055555556</v>
+        <v>46042.84583333333</v>
       </c>
       <c r="R9" s="2">
-        <v>46043.37708333333</v>
+        <v>46043.36319444444</v>
       </c>
       <c r="S9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I10">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="J10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L10" s="2">
-        <v>46042.57638888889</v>
+        <v>46042.71527777778</v>
       </c>
       <c r="M10">
         <v>90</v>
       </c>
       <c r="N10" s="2">
-        <v>46042.63888888889</v>
+        <v>46042.77777777778</v>
       </c>
       <c r="O10">
-        <v>298</v>
+        <v>170</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q10" s="2">
-        <v>46042.84583333333</v>
+        <v>46042.89583333334</v>
       </c>
       <c r="R10" s="2">
-        <v>46043.36319444444</v>
+        <v>46042.9375</v>
       </c>
       <c r="S10" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I11">
-        <v>4.5022</v>
+        <v>4.5088</v>
       </c>
       <c r="J11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L11" s="2">
-        <v>46042.63888888889</v>
+        <v>46042.79166666666</v>
       </c>
       <c r="M11">
         <v>90</v>
       </c>
       <c r="N11" s="2">
-        <v>46042.70138888889</v>
+        <v>46042.85416666666</v>
       </c>
       <c r="O11">
-        <v>245</v>
+        <v>660</v>
       </c>
       <c r="P11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q11" s="2">
-        <v>46042.87152777778</v>
+        <v>46043.3125</v>
       </c>
       <c r="R11" s="2">
-        <v>46043.79583333333</v>
+        <v>46043.50069444445</v>
       </c>
       <c r="S11" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I12">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="J12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L12" s="2">
-        <v>46042.71527777778</v>
+        <v>46042.85416666666</v>
       </c>
       <c r="M12">
         <v>90</v>
       </c>
       <c r="N12" s="2">
-        <v>46042.77777777778</v>
+        <v>46042.91666666666</v>
       </c>
       <c r="O12">
-        <v>170</v>
+        <v>643</v>
       </c>
       <c r="P12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="Q12" s="2">
-        <v>46042.89583333334</v>
+        <v>46043.36319444444</v>
       </c>
       <c r="R12" s="2">
-        <v>46042.9375</v>
+        <v>46043.54722222222</v>
       </c>
       <c r="S12" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
         <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I13">
-        <v>4.5088</v>
+        <v>4.4163</v>
       </c>
       <c r="J13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L13" s="2">
-        <v>46042.79166666666</v>
+        <v>46042.91666666666</v>
       </c>
       <c r="M13">
         <v>90</v>
       </c>
       <c r="N13" s="2">
-        <v>46042.85416666666</v>
+        <v>46042.97916666666</v>
       </c>
       <c r="O13">
-        <v>660</v>
+        <v>573</v>
       </c>
       <c r="P13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="Q13" s="2">
-        <v>46043.3125</v>
+        <v>46043.37708333333</v>
       </c>
       <c r="R13" s="2">
-        <v>46043.50069444445</v>
+        <v>46043.59027777778</v>
       </c>
       <c r="S13" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I14">
         <v>4.4185</v>
       </c>
       <c r="J14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L14" s="2">
-        <v>46042.85416666666</v>
+        <v>46043.38194444445</v>
       </c>
       <c r="M14">
         <v>90</v>
       </c>
       <c r="N14" s="2">
-        <v>46042.91666666666</v>
+        <v>46043.44444444445</v>
       </c>
       <c r="O14">
-        <v>643</v>
+        <v>148</v>
       </c>
       <c r="P14" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="Q14" s="2">
-        <v>46043.36319444444</v>
+        <v>46043.54722222222</v>
       </c>
       <c r="R14" s="2">
-        <v>46043.54722222222</v>
+        <v>46043.73055555556</v>
       </c>
       <c r="S14" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
@@ -2184,170 +2211,170 @@
         <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I15">
         <v>4.4163</v>
       </c>
       <c r="J15" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K15" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L15" s="2">
-        <v>46042.91666666666</v>
+        <v>46043.44444444445</v>
       </c>
       <c r="M15">
         <v>90</v>
       </c>
       <c r="N15" s="2">
-        <v>46042.97916666666</v>
+        <v>46043.50694444445</v>
       </c>
       <c r="O15">
-        <v>573</v>
+        <v>120</v>
       </c>
       <c r="P15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q15" s="2">
-        <v>46043.37708333333</v>
+        <v>46043.59027777778</v>
       </c>
       <c r="R15" s="2">
-        <v>46043.59027777778</v>
+        <v>46043.80416666667</v>
       </c>
       <c r="S15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H16" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I16">
-        <v>4.4185</v>
+        <v>4.5228</v>
       </c>
       <c r="J16" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K16" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L16" s="2">
-        <v>46043.38194444445</v>
+        <v>46043.50833333333</v>
       </c>
       <c r="M16">
         <v>90</v>
       </c>
       <c r="N16" s="2">
-        <v>46043.44444444445</v>
+        <v>46043.57083333333</v>
       </c>
       <c r="O16">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="Q16" s="2">
-        <v>46043.54722222222</v>
+        <v>46043.71180555555</v>
       </c>
       <c r="R16" s="2">
-        <v>46043.73055555556</v>
+        <v>46043.83194444444</v>
       </c>
       <c r="S16" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H17" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I17">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="J17" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K17" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L17" s="2">
-        <v>46043.44444444445</v>
+        <v>46043.58472222222</v>
       </c>
       <c r="M17">
         <v>90</v>
       </c>
       <c r="N17" s="2">
-        <v>46043.50694444445</v>
+        <v>46043.64722222222</v>
       </c>
       <c r="O17">
         <v>120</v>
       </c>
       <c r="P17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q17" s="2">
-        <v>46043.59027777778</v>
+        <v>46043.73055555556</v>
       </c>
       <c r="R17" s="2">
-        <v>46043.80416666667</v>
+        <v>46043.91458333333</v>
       </c>
       <c r="S17" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2358,164 +2385,164 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I18">
-        <v>4.5228</v>
+        <v>2.2511</v>
       </c>
       <c r="J18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L18" s="2">
-        <v>46043.50833333333</v>
+        <v>46041.39375</v>
       </c>
       <c r="M18">
         <v>90</v>
       </c>
       <c r="N18" s="2">
-        <v>46043.57083333333</v>
+        <v>46041.45625</v>
       </c>
       <c r="O18">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="P18" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="Q18" s="2">
-        <v>46043.71180555555</v>
+        <v>46041.53958333333</v>
       </c>
       <c r="R18" s="2">
-        <v>46043.83194444444</v>
+        <v>46042.50138888889</v>
       </c>
       <c r="S18" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I19">
-        <v>4.4185</v>
+        <v>0.5663</v>
       </c>
       <c r="J19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K19" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L19" s="2">
-        <v>46043.58472222222</v>
+        <v>46041.45625</v>
       </c>
       <c r="M19">
         <v>90</v>
       </c>
       <c r="N19" s="2">
-        <v>46043.64722222222</v>
+        <v>46041.51875</v>
       </c>
       <c r="O19">
-        <v>120</v>
+        <v>1415</v>
       </c>
       <c r="P19" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="Q19" s="2">
-        <v>46043.73055555556</v>
+        <v>46042.50138888889</v>
       </c>
       <c r="R19" s="2">
-        <v>46043.91458333333</v>
+        <v>46042.57569444444</v>
       </c>
       <c r="S19" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I20">
         <v>2.2511</v>
       </c>
       <c r="J20" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K20" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L20" s="2">
-        <v>46042.3125</v>
+        <v>46041.53263888889</v>
       </c>
       <c r="M20">
         <v>90</v>
       </c>
       <c r="N20" s="2">
-        <v>46042.375</v>
+        <v>46041.59513888889</v>
       </c>
       <c r="O20">
-        <v>289</v>
+        <v>1412</v>
       </c>
       <c r="P20" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="Q20" s="2">
         <v>46042.57569444444</v>
@@ -2524,7 +2551,7 @@
         <v>46042.87152777778</v>
       </c>
       <c r="S20" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -2535,55 +2562,55 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H21" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I21">
-        <v>2.2544</v>
+        <v>2.2511</v>
       </c>
       <c r="J21" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K21" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L21" s="2">
-        <v>46042.38888888889</v>
+        <v>46041.80902777778</v>
       </c>
       <c r="M21">
         <v>90</v>
       </c>
       <c r="N21" s="2">
-        <v>46042.45138888889</v>
+        <v>46041.87152777778</v>
       </c>
       <c r="O21">
-        <v>1511</v>
+        <v>1440</v>
       </c>
       <c r="P21" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="Q21" s="2">
-        <v>46043.50069444445</v>
+        <v>46042.87152777778</v>
       </c>
       <c r="R21" s="2">
-        <v>46043.59513888889</v>
+        <v>46043.5</v>
       </c>
       <c r="S21" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -2600,54 +2627,54 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H22" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I22">
-        <v>2.2348</v>
+        <v>2.2511</v>
       </c>
       <c r="J22" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K22" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L22" s="2">
-        <v>46042.46527777778</v>
+        <v>46042.4375</v>
       </c>
       <c r="M22">
         <v>90</v>
       </c>
       <c r="N22" s="2">
-        <v>46042.52777777778</v>
+        <v>46042.5</v>
       </c>
       <c r="O22">
-        <v>1580</v>
+        <v>1440</v>
       </c>
       <c r="P22" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="Q22" s="2">
-        <v>46043.625</v>
+        <v>46043.5</v>
       </c>
       <c r="R22" s="2">
-        <v>46043.71180555555</v>
+        <v>46043.79583333333</v>
       </c>
       <c r="S22" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>45</v>
@@ -2656,52 +2683,170 @@
         <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G23" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H23" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I23">
-        <v>2.2314</v>
+        <v>2.2544</v>
       </c>
       <c r="J23" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L23" s="2">
-        <v>46042.54166666666</v>
+        <v>46042.51388888889</v>
       </c>
       <c r="M23">
         <v>90</v>
       </c>
       <c r="N23" s="2">
-        <v>46042.60416666666</v>
+        <v>46042.57638888889</v>
       </c>
       <c r="O23">
-        <v>1768</v>
+        <v>1331</v>
       </c>
       <c r="P23" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="Q23" s="2">
+        <v>46043.50069444445</v>
+      </c>
+      <c r="R23" s="2">
+        <v>46043.59513888889</v>
+      </c>
+      <c r="S23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24">
+        <v>2.2348</v>
+      </c>
+      <c r="J24" t="s">
+        <v>107</v>
+      </c>
+      <c r="K24" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="2">
+        <v>46042.59027777778</v>
+      </c>
+      <c r="M24">
+        <v>90</v>
+      </c>
+      <c r="N24" s="2">
+        <v>46042.65277777778</v>
+      </c>
+      <c r="O24">
+        <v>1400</v>
+      </c>
+      <c r="P24" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>46043.625</v>
+      </c>
+      <c r="R24" s="2">
+        <v>46043.71180555555</v>
+      </c>
+      <c r="S24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25">
+        <v>2.2314</v>
+      </c>
+      <c r="J25" t="s">
+        <v>107</v>
+      </c>
+      <c r="K25" t="s">
+        <v>109</v>
+      </c>
+      <c r="L25" s="2">
+        <v>46042.76944444444</v>
+      </c>
+      <c r="M25">
+        <v>90</v>
+      </c>
+      <c r="N25" s="2">
+        <v>46042.83194444444</v>
+      </c>
+      <c r="O25">
+        <v>1440</v>
+      </c>
+      <c r="P25" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q25" s="2">
         <v>46043.83194444444</v>
       </c>
-      <c r="R23" s="2">
+      <c r="R25" s="2">
         <v>46044.06527777778</v>
       </c>
-      <c r="S23" t="s">
-        <v>120</v>
+      <c r="S25" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2721,1139 +2866,1163 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>237</v>
+        <v>110</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>237</v>
+        <v>110</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>237</v>
+        <v>110</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>246</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>246</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>247</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B31" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B32" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B35" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B41" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B44" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B46" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>256</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>243</v>
+        <v>110</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B59" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B60" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>247</v>
+        <v>254</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>255</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>256</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>256</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B78" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B79" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B80" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B81" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B82" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B83" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B84" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B85" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B86" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B87" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B88" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B89" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B90" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B91" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B92" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B93" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B94" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B98" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B100" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B109" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B110" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B111" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B112" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B113" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B114" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3873,3389 +4042,3578 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>260</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>266</v>
+        <v>122</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>237</v>
+        <v>110</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>237</v>
+        <v>110</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>237</v>
+        <v>110</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>264</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>264</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>264</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>264</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>264</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>264</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>264</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>264</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>266</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>266</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>238</v>
+        <v>266</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>238</v>
+        <v>266</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>238</v>
+        <v>266</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B29" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B30" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B42" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B43" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B44" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>239</v>
+        <v>264</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>239</v>
+        <v>303</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>298</v>
+        <v>266</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>306</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>292</v>
+        <v>248</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>240</v>
+        <v>266</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>306</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>292</v>
+        <v>248</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>240</v>
+        <v>266</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>306</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>292</v>
+        <v>248</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>291</v>
+        <v>312</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K55" s="3" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>292</v>
+        <v>248</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>258</v>
+        <v>312</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K56" s="3" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K57" s="3" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>245</v>
+        <v>306</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B59" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>245</v>
+        <v>306</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B60" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>244</v>
+        <v>307</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>301</v>
+        <v>253</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B77" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B78" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B79" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B80" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B81" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B82" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B83" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B84" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B85" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B86" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B87" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B88" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B89" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B90" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B91" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B92" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>257</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>257</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>302</v>
+        <v>267</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B98" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>257</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>302</v>
+        <v>267</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>257</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J99" s="3" t="s">
-        <v>302</v>
+        <v>267</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B100" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>257</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>303</v>
+        <v>267</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>257</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>303</v>
+        <v>267</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>257</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>303</v>
+        <v>267</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>296</v>
+        <v>268</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>303</v>
+        <v>267</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>296</v>
+        <v>268</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>303</v>
+        <v>267</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>253</v>
+        <v>268</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>303</v>
+        <v>267</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>253</v>
+        <v>268</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J106" s="3" t="s">
-        <v>303</v>
+        <v>267</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F107" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="G107" s="3" t="s">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>304</v>
+        <v>267</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C108" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="G108" s="3" t="s">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J108" s="3" t="s">
-        <v>304</v>
+        <v>267</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C109" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F109" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E109" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="G109" s="3" t="s">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J109" s="3" t="s">
-        <v>304</v>
+        <v>267</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B110" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C110" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F110" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E110" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="G110" s="3" t="s">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>304</v>
+        <v>267</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B111" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="G111" s="3" t="s">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J111" s="3" t="s">
-        <v>304</v>
+        <v>267</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B112" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C112" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F112" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E112" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="G112" s="3" t="s">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J112" s="3" t="s">
-        <v>304</v>
+        <v>267</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B113" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C113" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F113" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E113" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="G113" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>297</v>
+        <v>259</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
+        <v>279</v>
+      </c>
+      <c r="B114" t="s">
+        <v>109</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I114" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B114" t="s">
-        <v>106</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J114" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="K114" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="L114" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B115" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J115" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="K115" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B116" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="K116" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B117" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="K117" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B118" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="K118" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B119" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="K119" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B120" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="K120" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B121" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="K121" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B122" t="s">
-        <v>106</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>259</v>
+        <v>109</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B123" t="s">
-        <v>106</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>259</v>
+        <v>109</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B124" t="s">
-        <v>106</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>259</v>
+        <v>109</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B125" t="s">
-        <v>236</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B126" t="s">
-        <v>236</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B127" t="s">
-        <v>236</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B128" t="s">
-        <v>236</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
+        <v>245</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B129" t="s">
-        <v>236</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
+        <v>245</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B130" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B131" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B132" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -7265,7 +7623,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -7275,34 +7633,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7310,25 +7668,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7336,25 +7694,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7362,22 +7720,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J4" t="s">
         <v>48</v>
@@ -7388,25 +7746,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7414,22 +7772,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J6" t="s">
         <v>49</v>
@@ -7440,22 +7798,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J7" t="s">
         <v>48</v>
@@ -7466,25 +7824,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -7492,22 +7850,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J9" t="s">
         <v>48</v>
@@ -7518,25 +7876,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -7544,25 +7902,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -7570,25 +7928,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7596,25 +7954,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
         <v>94</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7622,25 +7980,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -7648,22 +8006,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J15" t="s">
         <v>52</v>
@@ -7674,25 +8032,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7700,25 +8058,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J17" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7726,25 +8084,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
         <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7752,25 +8110,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J19" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7778,25 +8136,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7804,25 +8162,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
         <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7830,13 +8188,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>67</v>
@@ -7845,7 +8203,7 @@
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J22" t="s">
         <v>56</v>
@@ -7856,25 +8214,77 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G23" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J23" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>327</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>327</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
